--- a/data/trans_orig/IP07B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07B-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores según su salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>28059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26790</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42295</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44306</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64673</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54135</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70261</t>
+          <t>70531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>73430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115517</t>
+          <t>115619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140274</t>
+          <t>139774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>31753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>25987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>34318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54121</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45180</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62208</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85918</t>
+          <t>87499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88688</t>
+          <t>88491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110082</t>
+          <t>108913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104722</t>
+          <t>104733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>125701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200896</t>
+          <t>199153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229694</t>
+          <t>231806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49354</t>
+          <t>49568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>71579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70200</t>
+          <t>69797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81319</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>111046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144794</t>
+          <t>142730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>149058</t>
+          <t>148734</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175001</t>
+          <t>175311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166420</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193474</t>
+          <t>193116</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322098</t>
+          <t>324773</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>360250</t>
+          <t>362301</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>68577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118263</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores según su salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>44754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>27848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44610</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58429</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83520</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70420</t>
+          <t>71449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89744</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71775</t>
+          <t>71076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90672</t>
+          <t>91111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148700</t>
+          <t>148490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176764</t>
+          <t>174618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>55892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30836</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>48181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>49603</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>66112</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92261</t>
+          <t>91515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75516</t>
+          <t>75383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96686</t>
+          <t>94963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71330</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91489</t>
+          <t>91168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152825</t>
+          <t>151881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180504</t>
+          <t>181283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>49131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73557</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86258</t>
+          <t>86929</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63508</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88789</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132284</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168315</t>
+          <t>167938</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>152939</t>
+          <t>153292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>180187</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>148479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177639</t>
+          <t>175897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>306806</t>
+          <t>309544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>347468</t>
+          <t>350592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>52746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>90933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>121135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores según su salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>30131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41074</t>
+          <t>41011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79111</t>
+          <t>78239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101003</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>52303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72753</t>
+          <t>72936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136765</t>
+          <t>137027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166193</t>
+          <t>167836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48866</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69456</t>
+          <t>69650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79151</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113701</t>
+          <t>111745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141703</t>
+          <t>142027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37350</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59844</t>
+          <t>59018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>61421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>83057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64324</t>
+          <t>63877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85391</t>
+          <t>84966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132203</t>
+          <t>133425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161805</t>
+          <t>163153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43396</t>
+          <t>42674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62078</t>
+          <t>61991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>74407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102165</t>
+          <t>101254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128961</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>64677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84241</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115265</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>147619</t>
+          <t>146168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177654</t>
+          <t>176316</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>121741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>151631</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>279496</t>
+          <t>277304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320525</t>
+          <t>320344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>97139</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>125365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116209</t>
+          <t>116630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146524</t>
+          <t>146405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>222609</t>
+          <t>220457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262948</t>
+          <t>263155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7689,82 +7689,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5026</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1623</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5680</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>3857</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>8856</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48162</t>
+          <t>48274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>51157</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73698</t>
+          <t>73534</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40421</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64879</t>
+          <t>64232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86701</t>
+          <t>88761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>36617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49714</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89814</t>
+          <t>89542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75064</t>
+          <t>75058</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125125</t>
+          <t>126116</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78603</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61816</t>
+          <t>59726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94435</t>
+          <t>94489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>104279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164439</t>
+          <t>165459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88907</t>
+          <t>89992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>46046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141948</t>
+          <t>135319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>70919</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128183</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129018</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>189335</t>
+          <t>187942</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56727</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113477</t>
+          <t>112788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100832</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139835</t>
+          <t>139047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179936</t>
+          <t>177327</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242548</t>
+          <t>241772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30692</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114978</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32264</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61784</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72309</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181440</t>
+          <t>181935</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07B-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7817</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1508</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5450</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4659</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3495</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33759</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26455</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41595</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27,91%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20416</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14625</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28059</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14832</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28765</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,78%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,81%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>33759</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>26237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42006</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44390</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>65430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -1062,72 +1062,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64812</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56059</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>73556</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>60,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>62362</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54178</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>70531</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>53353</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>69898</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>57,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>64,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>64812</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>55732</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>73430</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>53,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115619</t>
+          <t>114101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139774</t>
+          <t>139108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -1175,72 +1175,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18884</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24433</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18080</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31753</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18137</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>32571</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18884</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13358</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25987</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>35279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53180</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -1288,57 +1288,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>120950</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>120950</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>120950</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>108719</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>108719</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>108719</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>120950</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>120950</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>120950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1405,107 +1405,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4225</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3614</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4343</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3622</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1518,107 +1518,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3851</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8316</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7606</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2785</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>11383</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2140</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6094</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>10761</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1631,72 +1631,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35865</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27547</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45207</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37419</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29360</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>47256</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29260</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>47535</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21,45%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35865</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27974</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>44917</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60478</t>
+          <t>60901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87499</t>
+          <t>86825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1744,72 +1744,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115711</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>104507</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>125449</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>99625</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>88491</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108913</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>88619</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>110609</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>57,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>115711</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>104733</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>125701</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,85%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199153</t>
+          <t>199823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231806</t>
+          <t>230527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -1857,72 +1857,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27496</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20222</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36656</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32844</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25511</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41702</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25223</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41336</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>18,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27496</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19804</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35863</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>71735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -1970,57 +1970,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>181212</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181212</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181212</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>174465</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>174465</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>174465</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>181212</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>181212</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>181212</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2087,107 +2087,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4146</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3203</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2205,67 +2205,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10486</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>5359</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10069</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10295</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5634</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2507</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>11529</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2313,72 +2313,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>69624</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>58300</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>82795</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>19,29%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>57836</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>47484</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>69797</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>47443</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>69146</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>20,42%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>24,65%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>69624</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>58544</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>81807</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>111046</t>
+          <t>111439</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142730</t>
+          <t>143584</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -2426,72 +2426,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>180523</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>166066</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>194391</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>59,74%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>54,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>161986</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>148734</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>175311</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>147422</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>174680</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>57,2%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>52,52%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>61,91%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>180523</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>165446</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>193116</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>59,74%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>324773</t>
+          <t>323993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>362301</t>
+          <t>361778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -2539,72 +2539,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46381</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37074</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>56954</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>57277</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>47379</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>68577</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>46109</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>69039</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>20,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>46381</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>37186</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>56745</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>88492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118681</t>
+          <t>119306</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -2652,57 +2652,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>302162</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>302162</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>302162</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>421</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>283184</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>283184</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>283184</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>302162</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>302162</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>302162</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2831,7 +2831,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2999,107 +2999,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4051</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>682</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2784</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3429</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3112,72 +3112,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6287</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2932</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3015</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7271</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7591</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6287</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11520</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -3225,72 +3225,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35907</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27526</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>44877</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>35267</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26956</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>44754</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>26431</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44222</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>25,31%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>35907</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27848</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>44851</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,23%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60406</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>83434</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -3338,107 +3338,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>80960</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70645</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91979</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>54,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>62,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>80922</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>71449</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>90710</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>70714</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>90244</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>58,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>51,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>80960</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>71076</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>91111</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>54,63%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>64,75%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>161882</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>148490</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>176798</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>51,64%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>61,48%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>161882</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>148490</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>174618</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>56,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -3451,72 +3451,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24369</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18431</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33098</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20159</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13887</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27004</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14068</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>28078</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>14,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24369</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17024</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>31952</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55892</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -3564,57 +3564,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>148205</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>148205</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>148205</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>139363</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>139363</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>139363</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>148205</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>148205</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>148205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3681,107 +3681,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5133</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1443</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5047</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3799,67 +3799,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8683</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>4886</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9388</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4413</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39177</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30206</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>48407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>29,52%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38989</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29554</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48181</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>30124</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>48262</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>25,51%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>30232</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>49603</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66112</t>
+          <t>67142</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91515</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4020,72 +4020,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81253</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70767</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91969</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>56,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>85737</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>75383</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>94963</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>75310</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>95743</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>56,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>49,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>81253</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>70082</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>91168</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>49,54%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151881</t>
+          <t>152794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181283</t>
+          <t>180765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -4133,72 +4133,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39163</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30961</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48662</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>21791</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15562</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29753</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15394</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>29801</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>39163</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30871</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49131</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72671</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164007</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164007</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164007</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152846</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152846</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152846</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>164007</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>164007</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>164007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1443</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5006</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2977</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10700</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6339</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16537</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7901</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4374</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14599</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13627</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10700</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6558</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>16607</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>75085</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>63819</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88500</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>74256</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63296</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>86929</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>62469</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>86440</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>25,41%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>75085</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>62097</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>86620</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131934</t>
+          <t>131985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167938</t>
+          <t>166886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -4707,67 +4707,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>162213</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>147567</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>177838</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>51,96%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>47,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>166659</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>153292</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>178790</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>152753</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>180786</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>57,03%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>52,46%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>61,19%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>162213</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>148479</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>175897</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>51,96%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>309544</t>
+          <t>307430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>350592</t>
+          <t>349751</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>63532</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>52202</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>76675</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>24,56%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>41949</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>32686</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>52746</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>33325</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>52308</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>14,36%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>63532</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>52267</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>74765</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90933</t>
+          <t>90474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>312212</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>312212</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>312212</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>415</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>292209</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>292209</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>292209</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>312212</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>312212</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>312212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5107,7 +5107,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5275,72 +5275,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3919</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5393,67 +5393,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2416</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5734</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2416</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5501,72 +5501,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29632</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21540</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21600</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15513</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30131</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14905</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>29124</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29632</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22021</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38054</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41011</t>
+          <t>40277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>63303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -5614,72 +5614,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61823</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51654</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72377</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89306</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>78239</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>100191</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>79211</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>100149</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>51,85%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61823</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>52303</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72936</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137027</t>
+          <t>136199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167836</t>
+          <t>166104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>68637</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>57994</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79764</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>58725</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48652</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>69650</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>47926</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>69169</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>68637</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>57605</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78681</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>41,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111745</t>
+          <t>113065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142027</t>
+          <t>141871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -5840,57 +5840,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>163898</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>163898</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>163898</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>172235</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>172235</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>172235</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>163898</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>163898</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>163898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6070,72 +6070,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2446</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5986</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6183,72 +6183,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22574</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31826</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>24790</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17200</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33098</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17827</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>32595</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,32%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22574</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15933</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31767</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>59068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -6296,72 +6296,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74873</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64843</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85428</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72763</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>61421</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83057</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62614</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>83875</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>47,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>74873</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>63877</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84966</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>46,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133425</t>
+          <t>131885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163153</t>
+          <t>162879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -6409,72 +6409,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62920</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52761</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73959</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>51935</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>42674</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61991</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>42525</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>60916</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>62920</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>53267</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>74407</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101254</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>128560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -6522,57 +6522,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162107</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162107</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162107</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151933</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151933</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151933</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162107</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162107</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6639,72 +6639,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4828</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3256</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4202</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6752,72 +6752,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10064</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4394</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9008</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1880</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4156</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9903</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6865,107 +6865,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52207</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>66043</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>46390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>36801</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57718</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>36768</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>58503</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>52207</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>42018</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>64677</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>98596</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>83821</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>114360</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>12,89%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>98596</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>83959</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>115642</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -6978,72 +6978,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>136696</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>122119</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>152786</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>41,93%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>37,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>162068</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>146168</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>176316</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>146037</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>175355</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>50,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>45,09%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>54,39%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>136696</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>121741</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>151631</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>41,93%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>277304</t>
+          <t>277959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320344</t>
+          <t>321035</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -7091,72 +7091,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>131557</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>115210</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>146308</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>110659</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>97139</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>125365</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>97171</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>125411</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>34,14%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>38,67%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>131557</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>116630</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>146405</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>220457</t>
+          <t>221374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263155</t>
+          <t>262424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -7204,57 +7204,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326006</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326006</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326006</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>462</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>324168</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>324168</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>324168</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326006</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326006</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326006</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7383,7 +7383,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7664,72 +7664,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2234</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6124</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7739,32 +7739,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -7777,72 +7777,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39434</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31555</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48635</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,03%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>49,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>23110</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17003</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30020</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30931</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7852,32 +7852,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>64447</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51157</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>74914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -7890,72 +7890,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41565</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32110</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50066</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33307</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>26556</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42611</t>
+          <t>34879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33049</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51783</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7965,32 +7965,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>75918</t>
+          <t>76444</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>65719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88761</t>
+          <t>89014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -8003,72 +8003,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9897</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23498</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10105</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6137</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15974</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>26304</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36617</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -8116,57 +8116,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>68757</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>68757</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>68757</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>72542</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>72542</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>72542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>168122</t>
+          <t>171061</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>168122</t>
+          <t>171061</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>168122</t>
+          <t>171061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8346,72 +8346,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2277</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6554</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8421,32 +8421,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -8459,72 +8459,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>63726</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>49400</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>83596</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36,94%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34428</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18047</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46235</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>24,15%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>32,43%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64221</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50679</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89542</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8534,32 +8534,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>98649</t>
+          <t>100678</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75058</t>
+          <t>84281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>126116</t>
+          <t>123000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -8572,72 +8572,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79331</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62201</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>93554</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60987</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>31529</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>79164</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>42,78%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79577</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59726</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94489</t>
+          <t>75385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>140564</t>
+          <t>144419</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104279</t>
+          <t>124444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165459</t>
+          <t>161916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -8685,72 +8685,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27065</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17708</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42231</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>46716</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21855</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>89992</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27907</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>33874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8760,32 +8760,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>74623</t>
+          <t>50648</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135319</t>
+          <t>66670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -8798,57 +8798,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172488</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172488</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172488</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>173651</t>
+          <t>125982</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>173651</t>
+          <t>125982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>173651</t>
+          <t>125982</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8873,17 +8873,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>316198</t>
+          <t>298470</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>316198</t>
+          <t>298470</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>316198</t>
+          <t>298470</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9028,72 +9028,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3948</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8618</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7180</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9103,32 +9103,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9141,72 +9141,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>103160</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>124235</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>45,84%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>57538</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>35203</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>70919</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>103300</t>
+          <t>61965</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86687</t>
+          <t>50881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129687</t>
+          <t>73341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9216,32 +9216,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>160839</t>
+          <t>165125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128469</t>
+          <t>144839</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>187942</t>
+          <t>185698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -9254,72 +9254,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>120896</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>102316</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>136860</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>37,75%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>94294</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>61605</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>112788</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>44,62%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>29,15%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>122188</t>
+          <t>99968</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101574</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139047</t>
+          <t>111925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9329,32 +9329,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>216482</t>
+          <t>220864</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177327</t>
+          <t>199968</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>241772</t>
+          <t>240841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -9367,72 +9367,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43004</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31626</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58232</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>56822</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>31647</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>105389</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>26,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,98%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>49,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61686</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100781</t>
+          <t>76951</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73114</t>
+          <t>63022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181935</t>
+          <t>94802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -9480,57 +9480,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>271007</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>271007</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>271007</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>211304</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>211304</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>211304</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>273016</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>273016</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>273016</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9555,17 +9555,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>484320</t>
+          <t>469532</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>484320</t>
+          <t>469532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>484320</t>
+          <t>469532</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
